--- a/untranslated/downloads/data-excel/1.3.1.c.xlsx
+++ b/untranslated/downloads/data-excel/1.3.1.c.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC818D2-AC3B-43B9-84FE-41696AD3F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -47,25 +48,25 @@
     <t>калктын жалпы санына карата, пайыз менен</t>
   </si>
   <si>
-    <t>1.3.1.1f Калктын жалпы санына карата пенсия жана майыптык боюнча жөлөкпул алуучу адамдардын үлүшү</t>
-  </si>
-  <si>
-    <t>1.3.1.1f Proportion of persons receiving pensions and disability benefits to the total population</t>
-  </si>
-  <si>
     <t>Population receiving pensions and disability benefits, persons</t>
   </si>
   <si>
     <t>to the total population, percent</t>
   </si>
   <si>
-    <t>1.3.1.1f Доля лиц, получающих пенсии и пособия по инвалидности к общей численности населения</t>
+    <t>1.3.1.c Калктын жалпы санына карата пенсия жана майыптык боюнча жөлөкпул алуучу адамдардын үлүшү</t>
+  </si>
+  <si>
+    <t>1.3.1.c Доля лиц, получающих пенсии и пособия по инвалидности к общей численности населения</t>
+  </si>
+  <si>
+    <t>1.3.1.c Proportion of persons receiving pensions and disability benefits to the total population</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -148,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -190,6 +191,14 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -469,8 +478,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="36.28515625" style="1" customWidth="1"/>
@@ -478,15 +487,15 @@
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -501,7 +510,7 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -522,8 +531,9 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
+      <c r="U2" s="18"/>
     </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
@@ -584,8 +594,11 @@
       <c r="T3" s="12">
         <v>2023</v>
       </c>
+      <c r="U3" s="16">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
@@ -593,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="7">
         <v>114961</v>
@@ -646,8 +659,11 @@
       <c r="T4" s="13">
         <v>217222</v>
       </c>
+      <c r="U4" s="15">
+        <v>220563</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -655,7 +671,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="10">
         <v>2.1907494237803631</v>
@@ -707,6 +723,9 @@
       </c>
       <c r="T5" s="14">
         <v>2.9794303052841493</v>
+      </c>
+      <c r="U5" s="17">
+        <v>3.0343137662507464</v>
       </c>
     </row>
   </sheetData>
